--- a/artfynd/A 48329-2025 artfynd.xlsx
+++ b/artfynd/A 48329-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1030,6 +1030,113 @@
           <t>Linköpings kommuns naturvårdsprogram 2023</t>
         </is>
       </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128920670</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100820</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Murtorpet, Murtorpet, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>540291</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6466347</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vist</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Johan Holmgren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Johan Holmgren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 48329-2025 artfynd.xlsx
+++ b/artfynd/A 48329-2025 artfynd.xlsx
@@ -1036,7 +1036,7 @@
         <v>128920670</v>
       </c>
       <c r="B5" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 48329-2025 artfynd.xlsx
+++ b/artfynd/A 48329-2025 artfynd.xlsx
@@ -1036,7 +1036,7 @@
         <v>128920670</v>
       </c>
       <c r="B5" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 48329-2025 artfynd.xlsx
+++ b/artfynd/A 48329-2025 artfynd.xlsx
@@ -1036,7 +1036,7 @@
         <v>128920670</v>
       </c>
       <c r="B5" t="n">
-        <v>100839</v>
+        <v>100844</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 48329-2025 artfynd.xlsx
+++ b/artfynd/A 48329-2025 artfynd.xlsx
@@ -1036,7 +1036,7 @@
         <v>128920670</v>
       </c>
       <c r="B5" t="n">
-        <v>100844</v>
+        <v>100847</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 48329-2025 artfynd.xlsx
+++ b/artfynd/A 48329-2025 artfynd.xlsx
@@ -1036,7 +1036,7 @@
         <v>128920670</v>
       </c>
       <c r="B5" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 48329-2025 artfynd.xlsx
+++ b/artfynd/A 48329-2025 artfynd.xlsx
@@ -1036,7 +1036,7 @@
         <v>128920670</v>
       </c>
       <c r="B5" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 48329-2025 artfynd.xlsx
+++ b/artfynd/A 48329-2025 artfynd.xlsx
@@ -1036,7 +1036,7 @@
         <v>128920670</v>
       </c>
       <c r="B5" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 48329-2025 artfynd.xlsx
+++ b/artfynd/A 48329-2025 artfynd.xlsx
@@ -1036,7 +1036,7 @@
         <v>128920670</v>
       </c>
       <c r="B5" t="n">
-        <v>100866</v>
+        <v>100892</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 48329-2025 artfynd.xlsx
+++ b/artfynd/A 48329-2025 artfynd.xlsx
@@ -1036,7 +1036,7 @@
         <v>128920670</v>
       </c>
       <c r="B5" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 48329-2025 artfynd.xlsx
+++ b/artfynd/A 48329-2025 artfynd.xlsx
@@ -1036,7 +1036,7 @@
         <v>128920670</v>
       </c>
       <c r="B5" t="n">
-        <v>100894</v>
+        <v>100895</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 48329-2025 artfynd.xlsx
+++ b/artfynd/A 48329-2025 artfynd.xlsx
@@ -1036,7 +1036,7 @@
         <v>128920670</v>
       </c>
       <c r="B5" t="n">
-        <v>100895</v>
+        <v>100899</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 48329-2025 artfynd.xlsx
+++ b/artfynd/A 48329-2025 artfynd.xlsx
@@ -1036,7 +1036,7 @@
         <v>128920670</v>
       </c>
       <c r="B5" t="n">
-        <v>100899</v>
+        <v>100901</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 48329-2025 artfynd.xlsx
+++ b/artfynd/A 48329-2025 artfynd.xlsx
@@ -1036,7 +1036,7 @@
         <v>128920670</v>
       </c>
       <c r="B5" t="n">
-        <v>100901</v>
+        <v>100905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 48329-2025 artfynd.xlsx
+++ b/artfynd/A 48329-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110361600</v>
+        <v>110361598</v>
       </c>
       <c r="B2" t="n">
-        <v>29897</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4781</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>200985</v>
+        <v>102306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blanksvart trämyra</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lasius fuliginosus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Latreille, 1798)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lövskogar vid Murtorpet, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540287.3455354164</v>
+        <v>540287</v>
       </c>
       <c r="R2" t="n">
-        <v>6466349.989153815</v>
+        <v>6466348</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +748,9 @@
           <t>2022-05-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-05-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110361599</v>
+        <v>110361600</v>
       </c>
       <c r="B3" t="n">
-        <v>39615</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>30288</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,39 +792,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>214803</v>
+        <v>200985</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Blanksvart trämyra</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Lasius fuliginosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Latreille, 1798)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lövskogar vid Murtorpet, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540287.3455354164</v>
+        <v>540288</v>
       </c>
       <c r="R3" t="n">
-        <v>6466349.989153815</v>
+        <v>6466350</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,19 +849,9 @@
           <t>2022-05-13</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-05-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,15 +882,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110361598</v>
+        <v>110361599</v>
       </c>
       <c r="B4" t="n">
-        <v>4717</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>40300</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -928,21 +893,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102306</v>
+        <v>214803</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -957,10 +922,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540286.3150331192</v>
+        <v>540288</v>
       </c>
       <c r="R4" t="n">
-        <v>6466347.878365949</v>
+        <v>6466350</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,19 +955,9 @@
           <t>2022-05-13</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-05-13</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,7 +991,7 @@
         <v>128920670</v>
       </c>
       <c r="B5" t="n">
-        <v>100905</v>
+        <v>101325</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 48329-2025 artfynd.xlsx
+++ b/artfynd/A 48329-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Linköpings kommuns naturvårdsprogram 2023</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110361598</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
           <t>Linköpings kommuns naturvårdsprogram 2023</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110361600</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -985,6 +1000,11 @@
           <t>Linköpings kommuns naturvårdsprogram 2023</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110361599</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,8 +1112,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128920670</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>